--- a/output/pdf_financials_xlsx/NRN.xlsx
+++ b/output/pdf_financials_xlsx/NRN.xlsx
@@ -6072,49 +6072,49 @@
         <v>1.034821</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.484555</v>
+        <v>1.481055</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.952795</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.658193</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.942418</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.951918</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.972078</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.650808</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.914433</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.872206</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.445231</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.502259</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.562838</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.741175</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.741552</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.85899</v>
       </c>
     </row>
     <row r="93">
@@ -7621,16 +7621,16 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-1.970206</v>
+        <v>-1.962351</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>-0.217433</v>
+        <v>-0.21092</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>-0.360444</v>
+        <v>-0.356191</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>-0.716566</v>
+        <v>-0.713101</v>
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
@@ -10246,7 +10246,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -14754,7 +14758,11 @@
           <t>Reserves 1,952,795</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -17557,7 +17565,11 @@
           <t>Amortization included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NRN.xlsx
+++ b/output/pdf_financials_xlsx/NRN.xlsx
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003415</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>4.8e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003266</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.033861</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.086505</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2151,28 +2151,28 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.629122</v>
+        <v>-1.629137</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.012335</v>
+        <v>-1.012383</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.252175</v>
+        <v>-1.255441</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.889737</v>
+        <v>-1.889775</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.233039</v>
+        <v>-0.2669</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.610053</v>
+        <v>-0.61006</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.991232</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.187863</v>
+        <v>-3.274368</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-0.69323</v>
@@ -2275,28 +2275,28 @@
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.629122</v>
+        <v>-1.629137</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.012335</v>
+        <v>-1.012383</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.252175</v>
+        <v>-1.255441</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.889737</v>
+        <v>-1.889775</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.233039</v>
+        <v>-0.2669</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.610053</v>
+        <v>-0.61006</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.991232</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.187863</v>
+        <v>-3.274368</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-0.69323</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.163968</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.365412</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.415412</v>
@@ -2581,40 +2581,40 @@
         <v>0.919546</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.349719</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.709825</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.128691</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.411145</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.101275</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.039011</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.244626</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.301621</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.216977</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.175532</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.386939</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.784654</v>
       </c>
     </row>
     <row r="35">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.163968</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.365412</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.415412</v>
@@ -2697,40 +2697,40 @@
         <v>0.919546</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.349719</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.709825</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.128691</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.411145</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.101275</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.039011</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.244626</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.301621</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.216977</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.175532</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.386939</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.784654</v>
       </c>
     </row>
     <row r="37">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.230153</v>
+        <v>0.06618499999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.392523</v>
+        <v>0.027111</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.027111</v>
@@ -3393,40 +3393,40 @@
         <v>0.195894</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.414387</v>
+        <v>0.064668</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.8196</v>
+        <v>0.109775</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.149764</v>
+        <v>0.021073</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.533981</v>
+        <v>0.122836</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.237621</v>
+        <v>0.136346</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.245953</v>
+        <v>0.206942</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.410587</v>
+        <v>0.165961</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.373722</v>
+        <v>0.072101</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.321321</v>
+        <v>0.104344</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.275401</v>
+        <v>0.099869</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.455786</v>
+        <v>0.06884700000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.971649</v>
+        <v>0.186995</v>
       </c>
     </row>
     <row r="49">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">

--- a/output/pdf_financials_xlsx/NRN.xlsx
+++ b/output/pdf_financials_xlsx/NRN.xlsx
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.032495</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.032495</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>0.048572</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.245675</v>
+        <v>0.21318</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>0.020028</v>
@@ -5358,10 +5358,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M80" s="3" t="n">
+        <v>0.01360280805158979</v>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
@@ -11350,7 +11348,11 @@
           <t>Current portion of lease obligation (Note 12)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -23914,7 +23916,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>-0.152178</v>
       </c>
@@ -29846,7 +29852,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30650,7 +30660,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E227" s="5" t="n">
         <v>0.152178</v>
       </c>
